--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4dd7ded1e4b445bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcd645b9dd0b04729"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rbb302400461c432c"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R2031b8e686e148ee"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcd645b9dd0b04729"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96e5055e766742dc"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R2031b8e686e148ee"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rd58051a7b61d451a"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96e5055e766742dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e53d7e497624edf"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rd58051a7b61d451a"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R6d4701e7319945da"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e53d7e497624edf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1d2d48a8f661401f"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R6d4701e7319945da"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rd812c374218b435b"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1d2d48a8f661401f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1bb5901d62414794"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rd812c374218b435b"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R398ee4297e7a4857"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1bb5901d62414794"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R38765a86cb6746bd"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R398ee4297e7a4857"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R9d6ebfb125614811"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R38765a86cb6746bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5a90698c1581415d"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R9d6ebfb125614811"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R053f8b05f1ae47c7"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5a90698c1581415d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc51d7fdf455d4ae4"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R053f8b05f1ae47c7"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Ra2a119de001647dd"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc51d7fdf455d4ae4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9aa236516598487b"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Ra2a119de001647dd"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R8c34cab9b0f44971"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9aa236516598487b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1b722bfbd6344164"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R8c34cab9b0f44971"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R0f3b74fb0c344d91"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1b722bfbd6344164"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3d16b0af11d448fc"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R0f3b74fb0c344d91"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R9908453a3a3f47a5"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3d16b0af11d448fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb182dfb2f3e644f8"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R9908453a3a3f47a5"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rb53abe90c10f48f2"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb182dfb2f3e644f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R93b1c825a90f4ad2"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rb53abe90c10f48f2"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R45515d27e01f4c46"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R93b1c825a90f4ad2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R958d630b9212464d"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R45515d27e01f4c46"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rdc801e13766f4cb0"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R958d630b9212464d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8f22da63e6bb4718"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rdc801e13766f4cb0"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R064ed3ee20534130"/>
   </x:pivotCaches>
 </x:workbook>
 </file>
